--- a/CreationOngletTest/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/CreationOngletTest/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T14:57:07+00:00</t>
+    <t>2024-06-12T15:37:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
